--- a/Proyectores QR.xlsx
+++ b/Proyectores QR.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2smra\Downloads\proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC948561-3B63-4175-92E8-84C85716434A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B7D42A-88BC-4E4D-9B80-513D3B890BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25485" yWindow="2565" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25485" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tareas" sheetId="14" r:id="rId1"/>
-    <sheet name="Aula 8 " sheetId="2" r:id="rId2"/>
-    <sheet name="Proyectores Aulas" sheetId="15" r:id="rId3"/>
+    <sheet name="Proyectores Aulas" sheetId="15" r:id="rId1"/>
+    <sheet name="Tareas" sheetId="14" r:id="rId2"/>
+    <sheet name="Aula 8 " sheetId="2" r:id="rId3"/>
     <sheet name="Aulas informatica" sheetId="9" r:id="rId4"/>
     <sheet name="Inventario de Almacenees" sheetId="12" r:id="rId5"/>
     <sheet name="Inventario Tecnologia" sheetId="16" r:id="rId6"/>
@@ -3855,6 +3855,55 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>-47625</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86DD2B0F-D4A9-ABEA-07FC-88EB0EAEA764}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="-47625" y="0"/>
+          <a:ext cx="47625" cy="38100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
@@ -3888,55 +3937,6 @@
         <a:xfrm>
           <a:off x="9525" y="7800975"/>
           <a:ext cx="6457950" cy="4133850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>-47625</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 65">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86DD2B0F-D4A9-ABEA-07FC-88EB0EAEA764}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="-47625" y="0"/>
-          <a:ext cx="47625" cy="38100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5066,2538 +5066,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA83E0C7-43EE-4D93-BFE2-EF890D1C7A82}">
-  <sheetPr>
-    <tabColor rgb="FFC00000"/>
-  </sheetPr>
-  <dimension ref="A1:L117"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="35" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="25"/>
-      <c r="G2" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="26"/>
-      <c r="G4" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="26"/>
-      <c r="G7" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="G8" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="26"/>
-      <c r="G9" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="26"/>
-      <c r="G10" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="28" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="26"/>
-      <c r="G16" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="K16" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="K17" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H18" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="I19" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H20" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="I22" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K23" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="K24" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="K25" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="I26" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="K26" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H27" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="I27" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H28" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="I28" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="K28" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" s="26"/>
-      <c r="G29" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="I29" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K29" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="I30" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="K30" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="26"/>
-      <c r="G31" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="H31" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="I31" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="K31" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="B32" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" s="26"/>
-      <c r="G32" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="H32" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="I32" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="K32" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="B33" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="G33" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="H33" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="I33" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="K33" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>134</v>
-      </c>
-      <c r="B34" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G34" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="H34" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K34" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>138</v>
-      </c>
-      <c r="B35" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="G35" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H35" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K35" s="28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>142</v>
-      </c>
-      <c r="B36" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="G36" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H36" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="I36" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K36" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>146</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="H37" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="J37" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K37" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="H38" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="J38" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K38" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="H39" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="J39" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K39" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>156</v>
-      </c>
-      <c r="B40" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="H40" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="J40" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K40" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>159</v>
-      </c>
-      <c r="B41" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="C41" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" s="26"/>
-      <c r="G41" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="H41" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="I41" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K41" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>163</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D42" s="26"/>
-      <c r="G42" s="34" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>166</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="C43" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="26"/>
-      <c r="G43" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="H43" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="J43" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K43" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>171</v>
-      </c>
-      <c r="B44" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="C44" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="D44" s="26"/>
-      <c r="G44" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H44" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J44" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K44" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>174</v>
-      </c>
-      <c r="B45" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="C45" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="D45" s="26"/>
-      <c r="G45" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H45" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="J45" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K45" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>177</v>
-      </c>
-      <c r="B46" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="C46" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="D46" s="26"/>
-      <c r="G46" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H46" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="J46" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="K46" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="D47" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="K47" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>182</v>
-      </c>
-      <c r="B48" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="C48" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="H48" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="I48" s="26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>186</v>
-      </c>
-      <c r="B49" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="D49" s="26"/>
-      <c r="H49" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="I49" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J49" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="K49" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>190</v>
-      </c>
-      <c r="B50" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D50" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="G50" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="H50" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="I50" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J50" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="K50" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>194</v>
-      </c>
-      <c r="B51" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D51" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G51" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="H51" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="I51" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J51" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="K51" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>197</v>
-      </c>
-      <c r="B52" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="D52" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G52" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="H52" s="34" t="s">
-        <v>201</v>
-      </c>
-      <c r="I52" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="K52" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>202</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>203</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="D53" s="26"/>
-      <c r="G53" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="H53" s="34" t="s">
-        <v>204</v>
-      </c>
-      <c r="I53" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J53" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="K53" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>205</v>
-      </c>
-      <c r="B54" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="C54" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="D54" s="26"/>
-      <c r="H54" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="I54" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="K54" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>208</v>
-      </c>
-      <c r="B55" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="C55" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D55" s="26"/>
-      <c r="G55" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="H55" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="I55" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="K55" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>211</v>
-      </c>
-      <c r="B56" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="C56" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="D56" s="26"/>
-      <c r="H56" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="I56" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="K56" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="L56" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>216</v>
-      </c>
-      <c r="B57" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="C57" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="D57" s="26"/>
-      <c r="G57" s="34" t="s">
-        <v>219</v>
-      </c>
-      <c r="H57" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="I57" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="K57" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="L57" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>222</v>
-      </c>
-      <c r="B58" s="34" t="s">
-        <v>223</v>
-      </c>
-      <c r="C58" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="D58" s="26"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>224</v>
-      </c>
-      <c r="B59" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="C59" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="D59" s="26"/>
-      <c r="H59" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="I59" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>227</v>
-      </c>
-      <c r="B60" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="C60" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="D60" s="26"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>230</v>
-      </c>
-      <c r="B61" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="C61" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="D61" s="26"/>
-      <c r="H61" s="34" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>233</v>
-      </c>
-      <c r="B62" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="D62" s="26"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>235</v>
-      </c>
-      <c r="B63" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="D63" s="26"/>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>237</v>
-      </c>
-      <c r="B64" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="D64" s="26"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>239</v>
-      </c>
-      <c r="B65" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="C65" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="D65" s="26"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>242</v>
-      </c>
-      <c r="B66" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="C66" s="34" t="s">
-        <v>244</v>
-      </c>
-      <c r="D66" s="26"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>245</v>
-      </c>
-      <c r="B67" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="C67" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="D67" s="26"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>247</v>
-      </c>
-      <c r="B68" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="C68" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="D68" s="26" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>250</v>
-      </c>
-      <c r="B69" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="C69" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="D69" s="26" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>252</v>
-      </c>
-      <c r="B70" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="C70" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="D70" s="26" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>255</v>
-      </c>
-      <c r="B71" s="34" t="s">
-        <v>256</v>
-      </c>
-      <c r="C71" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="D71" s="26" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B72" s="34" t="s">
-        <v>919</v>
-      </c>
-      <c r="C72" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="D72" s="26"/>
-      <c r="K72" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B73" s="34" t="s">
-        <v>920</v>
-      </c>
-      <c r="C73" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="D73" s="26"/>
-      <c r="K73" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D74" s="26"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D75" s="26"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D76" s="26"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D77" s="26"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D78" s="26"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D79" s="26"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D80" s="26"/>
-    </row>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D81" s="26"/>
-    </row>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D82" s="26"/>
-    </row>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D83" s="26"/>
-    </row>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D84" s="26"/>
-    </row>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D85" s="26"/>
-    </row>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D86" s="26"/>
-    </row>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D87" s="26"/>
-    </row>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D88" s="26"/>
-    </row>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D89" s="26"/>
-    </row>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D90" s="26"/>
-    </row>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D91" s="26"/>
-    </row>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D92" s="26"/>
-    </row>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D93" s="26"/>
-    </row>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D94" s="26"/>
-    </row>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D95" s="26"/>
-    </row>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D96" s="26"/>
-    </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D97" s="26"/>
-    </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D98" s="26"/>
-    </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D99" s="26"/>
-    </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D100" s="26"/>
-    </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D101" s="26"/>
-    </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D102" s="26"/>
-    </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D103" s="26"/>
-    </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D104" s="26"/>
-    </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D105" s="26"/>
-    </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D106" s="26"/>
-    </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D107" s="26"/>
-    </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D108" s="26"/>
-    </row>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D109" s="26"/>
-    </row>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D110" s="26"/>
-    </row>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D111" s="26"/>
-    </row>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D112" s="26"/>
-    </row>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D113" s="26"/>
-    </row>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D114" s="26"/>
-    </row>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D115" s="26"/>
-    </row>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D116" s="26"/>
-    </row>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D117" s="26"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K48 K58:K1048576" xr:uid="{30FB5F80-F4AF-4628-89CC-4EAFE2BEF007}">
-      <formula1>$K:$K</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576 K49:K57" xr:uid="{9BA59194-CE4B-473B-9048-91E3DC23A21D}">
-      <formula1>$I:$I</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B1FE39-02BA-4F34-8647-1063A59CB884}">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:K54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="70.85546875" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="B1" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>270</v>
-      </c>
-      <c r="C4" t="s">
-        <v>271</v>
-      </c>
-      <c r="D4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D6" t="s">
-        <v>278</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C7" t="s">
-        <v>280</v>
-      </c>
-      <c r="D7" t="s">
-        <v>281</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>282</v>
-      </c>
-      <c r="C8" t="s">
-        <v>283</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>284</v>
-      </c>
-      <c r="C9" t="s">
-        <v>285</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>288</v>
-      </c>
-      <c r="C10" t="s">
-        <v>289</v>
-      </c>
-      <c r="D10" t="s">
-        <v>290</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>291</v>
-      </c>
-      <c r="C11" t="s">
-        <v>292</v>
-      </c>
-      <c r="D11" t="s">
-        <v>293</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A12" s="6">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>294</v>
-      </c>
-      <c r="C12" t="s">
-        <v>295</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="8"/>
-      <c r="G12" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C13" t="s">
-        <v>298</v>
-      </c>
-      <c r="D13" t="s">
-        <v>299</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A14" s="6">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>300</v>
-      </c>
-      <c r="C14" t="s">
-        <v>301</v>
-      </c>
-      <c r="D14" t="s">
-        <v>302</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>303</v>
-      </c>
-      <c r="C15" t="s">
-        <v>304</v>
-      </c>
-      <c r="D15" t="s">
-        <v>305</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A16" s="6">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>306</v>
-      </c>
-      <c r="C16" t="s">
-        <v>307</v>
-      </c>
-      <c r="D16" t="s">
-        <v>308</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>309</v>
-      </c>
-      <c r="C17" t="s">
-        <v>310</v>
-      </c>
-      <c r="D17" t="s">
-        <v>308</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>311</v>
-      </c>
-      <c r="C18" t="s">
-        <v>312</v>
-      </c>
-      <c r="D18" t="s">
-        <v>313</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>314</v>
-      </c>
-      <c r="C19" t="s">
-        <v>315</v>
-      </c>
-      <c r="D19" t="s">
-        <v>316</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A20" s="6">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>317</v>
-      </c>
-      <c r="C20" t="s">
-        <v>318</v>
-      </c>
-      <c r="D20" t="s">
-        <v>319</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>320</v>
-      </c>
-      <c r="C21" t="s">
-        <v>321</v>
-      </c>
-      <c r="D21" t="s">
-        <v>322</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>323</v>
-      </c>
-      <c r="C22" t="s">
-        <v>324</v>
-      </c>
-      <c r="D22" t="s">
-        <v>325</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="6">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>326</v>
-      </c>
-      <c r="C23" t="s">
-        <v>327</v>
-      </c>
-      <c r="D23" t="s">
-        <v>319</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A24" s="6">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>328</v>
-      </c>
-      <c r="D24" t="s">
-        <v>329</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A25" s="6">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>330</v>
-      </c>
-      <c r="C25" t="s">
-        <v>331</v>
-      </c>
-      <c r="D25" t="s">
-        <v>332</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A26" s="6">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>333</v>
-      </c>
-      <c r="C26" t="s">
-        <v>334</v>
-      </c>
-      <c r="D26" t="s">
-        <v>335</v>
-      </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="4"/>
-    </row>
-    <row r="29" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="I29" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>336</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="I30" t="s">
-        <v>264</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I31" t="s">
-        <v>267</v>
-      </c>
-      <c r="J31" t="s">
-        <v>268</v>
-      </c>
-      <c r="K31" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I32" t="s">
-        <v>270</v>
-      </c>
-      <c r="J32" t="s">
-        <v>271</v>
-      </c>
-      <c r="K32" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="33" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I33" t="s">
-        <v>273</v>
-      </c>
-      <c r="J33" t="s">
-        <v>274</v>
-      </c>
-      <c r="K33" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="34" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I34" t="s">
-        <v>276</v>
-      </c>
-      <c r="J34" t="s">
-        <v>277</v>
-      </c>
-      <c r="K34" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="35" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I35" t="s">
-        <v>279</v>
-      </c>
-      <c r="J35" t="s">
-        <v>280</v>
-      </c>
-      <c r="K35" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="36" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I36" t="s">
-        <v>282</v>
-      </c>
-      <c r="J36" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="37" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I37" t="s">
-        <v>284</v>
-      </c>
-      <c r="J37" t="s">
-        <v>285</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="38" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I38" t="s">
-        <v>288</v>
-      </c>
-      <c r="J38" t="s">
-        <v>289</v>
-      </c>
-      <c r="K38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="39" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I39" t="s">
-        <v>291</v>
-      </c>
-      <c r="J39" t="s">
-        <v>292</v>
-      </c>
-      <c r="K39" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="40" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I40" t="s">
-        <v>294</v>
-      </c>
-      <c r="J40" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="41" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I41" t="s">
-        <v>297</v>
-      </c>
-      <c r="J41" t="s">
-        <v>298</v>
-      </c>
-      <c r="K41" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="42" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I42" t="s">
-        <v>300</v>
-      </c>
-      <c r="J42" t="s">
-        <v>301</v>
-      </c>
-      <c r="K42" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="43" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I43" t="s">
-        <v>303</v>
-      </c>
-      <c r="J43" t="s">
-        <v>304</v>
-      </c>
-      <c r="K43" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="44" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I44" t="s">
-        <v>306</v>
-      </c>
-      <c r="J44" t="s">
-        <v>307</v>
-      </c>
-      <c r="K44" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="45" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I45" t="s">
-        <v>309</v>
-      </c>
-      <c r="J45" t="s">
-        <v>310</v>
-      </c>
-      <c r="K45" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="46" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I46" t="s">
-        <v>311</v>
-      </c>
-      <c r="J46" t="s">
-        <v>312</v>
-      </c>
-      <c r="K46" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="47" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I47" t="s">
-        <v>314</v>
-      </c>
-      <c r="J47" t="s">
-        <v>315</v>
-      </c>
-      <c r="K47" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="48" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I48" t="s">
-        <v>317</v>
-      </c>
-      <c r="J48" t="s">
-        <v>318</v>
-      </c>
-      <c r="K48" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I49" t="s">
-        <v>320</v>
-      </c>
-      <c r="J49" t="s">
-        <v>321</v>
-      </c>
-      <c r="K49" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I50" t="s">
-        <v>323</v>
-      </c>
-      <c r="J50" t="s">
-        <v>324</v>
-      </c>
-      <c r="K50" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I51" t="s">
-        <v>326</v>
-      </c>
-      <c r="J51" t="s">
-        <v>327</v>
-      </c>
-      <c r="K51" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I52" t="s">
-        <v>62</v>
-      </c>
-      <c r="J52" t="s">
-        <v>328</v>
-      </c>
-      <c r="K52" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>338</v>
-      </c>
-      <c r="I53" t="s">
-        <v>330</v>
-      </c>
-      <c r="J53" t="s">
-        <v>331</v>
-      </c>
-      <c r="K53" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>339</v>
-      </c>
-      <c r="I54" t="s">
-        <v>333</v>
-      </c>
-      <c r="J54" t="s">
-        <v>334</v>
-      </c>
-      <c r="K54" t="s">
-        <v>335</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5115FC46-CF04-4132-9B66-D858947101FB}">
   <sheetPr>
     <tabColor theme="5"/>
@@ -9163,6 +6631,2538 @@
   <tableParts count="1">
     <tablePart r:id="rId77"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA83E0C7-43EE-4D93-BFE2-EF890D1C7A82}">
+  <sheetPr>
+    <tabColor rgb="FFC00000"/>
+  </sheetPr>
+  <dimension ref="A1:L117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="35" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="25"/>
+      <c r="G2" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="26"/>
+      <c r="G4" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="G7" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="G8" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="G9" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="26"/>
+      <c r="G10" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="G16" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="33"/>
+      <c r="D27" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="H27" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K28" s="28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="26"/>
+      <c r="G29" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="I30" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="K30" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="26"/>
+      <c r="G31" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="I31" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="26"/>
+      <c r="G32" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="I32" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="K32" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="H33" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="K33" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K34" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H35" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="I35" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K35" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H36" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="I36" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K36" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="J37" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K37" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="J38" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K38" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="J39" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K39" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="J40" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K40" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="26"/>
+      <c r="G41" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="H41" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K41" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D42" s="26"/>
+      <c r="G42" s="34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>166</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="26"/>
+      <c r="G43" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="H43" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="J43" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K43" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="26"/>
+      <c r="G44" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H44" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="J44" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K44" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D45" s="26"/>
+      <c r="G45" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H45" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="J45" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K45" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>177</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="C46" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D46" s="26"/>
+      <c r="G46" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H46" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="J46" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="K46" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="K47" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="I48" s="26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="26"/>
+      <c r="H49" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="I49" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="K49" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="G50" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="H50" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="I50" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="K50" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="H51" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="I51" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="K51" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="C52" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="H52" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="I52" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="K52" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>202</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="D53" s="26"/>
+      <c r="G53" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H53" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="I53" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="K53" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>205</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" s="26"/>
+      <c r="H54" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="I54" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J54" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="K54" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>208</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D55" s="26"/>
+      <c r="G55" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="H55" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="I55" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J55" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="K55" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>211</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="26"/>
+      <c r="H56" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="I56" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="K56" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="L56" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>216</v>
+      </c>
+      <c r="B57" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" s="26"/>
+      <c r="G57" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="H57" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="I57" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="K57" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="L57" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>222</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="D58" s="26"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>224</v>
+      </c>
+      <c r="B59" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="D59" s="26"/>
+      <c r="H59" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="I59" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>227</v>
+      </c>
+      <c r="B60" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="D60" s="26"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="D61" s="26"/>
+      <c r="H61" s="34" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>233</v>
+      </c>
+      <c r="B62" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="D62" s="26"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>235</v>
+      </c>
+      <c r="B63" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="D63" s="26"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>237</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="D64" s="26"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>239</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="D65" s="26"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>242</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="D66" s="26"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>245</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" s="26"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>247</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="C68" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>250</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>252</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="D70" s="26" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>255</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="C71" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="D71" s="26" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B72" s="34" t="s">
+        <v>919</v>
+      </c>
+      <c r="C72" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="D72" s="26"/>
+      <c r="K72" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B73" s="34" t="s">
+        <v>920</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="D73" s="26"/>
+      <c r="K73" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D74" s="26"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D75" s="26"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D76" s="26"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D77" s="26"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D78" s="26"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D79" s="26"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D80" s="26"/>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D81" s="26"/>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D82" s="26"/>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D83" s="26"/>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D84" s="26"/>
+    </row>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D85" s="26"/>
+    </row>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D86" s="26"/>
+    </row>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D87" s="26"/>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D88" s="26"/>
+    </row>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D89" s="26"/>
+    </row>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D90" s="26"/>
+    </row>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D91" s="26"/>
+    </row>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D92" s="26"/>
+    </row>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D93" s="26"/>
+    </row>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D94" s="26"/>
+    </row>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D95" s="26"/>
+    </row>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D96" s="26"/>
+    </row>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D97" s="26"/>
+    </row>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D98" s="26"/>
+    </row>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D99" s="26"/>
+    </row>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D100" s="26"/>
+    </row>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D101" s="26"/>
+    </row>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D102" s="26"/>
+    </row>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D103" s="26"/>
+    </row>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D104" s="26"/>
+    </row>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D105" s="26"/>
+    </row>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D106" s="26"/>
+    </row>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D107" s="26"/>
+    </row>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D108" s="26"/>
+    </row>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D109" s="26"/>
+    </row>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D110" s="26"/>
+    </row>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D111" s="26"/>
+    </row>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D112" s="26"/>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D113" s="26"/>
+    </row>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D114" s="26"/>
+    </row>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D115" s="26"/>
+    </row>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D116" s="26"/>
+    </row>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D117" s="26"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K48 K58:K1048576" xr:uid="{30FB5F80-F4AF-4628-89CC-4EAFE2BEF007}">
+      <formula1>$K:$K</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576 K49:K57" xr:uid="{9BA59194-CE4B-473B-9048-91E3DC23A21D}">
+      <formula1>$I:$I</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B1FE39-02BA-4F34-8647-1063A59CB884}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:K54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="70.85546875" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="B1" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="6">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A3" s="6">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D5" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A6" s="6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A7" s="6">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C8" t="s">
+        <v>283</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A9" s="6">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D11" t="s">
+        <v>293</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C12" t="s">
+        <v>295</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="8"/>
+      <c r="G12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A13" s="6">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" t="s">
+        <v>298</v>
+      </c>
+      <c r="D13" t="s">
+        <v>299</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A15" s="6">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>303</v>
+      </c>
+      <c r="C15" t="s">
+        <v>304</v>
+      </c>
+      <c r="D15" t="s">
+        <v>305</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+      <c r="A16" s="6">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" t="s">
+        <v>308</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>309</v>
+      </c>
+      <c r="C17" t="s">
+        <v>310</v>
+      </c>
+      <c r="D17" t="s">
+        <v>308</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A18" s="6">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" t="s">
+        <v>312</v>
+      </c>
+      <c r="D18" t="s">
+        <v>313</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" t="s">
+        <v>315</v>
+      </c>
+      <c r="D19" t="s">
+        <v>316</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A20" s="6">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" t="s">
+        <v>318</v>
+      </c>
+      <c r="D20" t="s">
+        <v>319</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A21" s="6">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>320</v>
+      </c>
+      <c r="C21" t="s">
+        <v>321</v>
+      </c>
+      <c r="D21" t="s">
+        <v>322</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A22" s="6">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>323</v>
+      </c>
+      <c r="C22" t="s">
+        <v>324</v>
+      </c>
+      <c r="D22" t="s">
+        <v>325</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>326</v>
+      </c>
+      <c r="C23" t="s">
+        <v>327</v>
+      </c>
+      <c r="D23" t="s">
+        <v>319</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A24" s="6">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="s">
+        <v>328</v>
+      </c>
+      <c r="D24" t="s">
+        <v>329</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>330</v>
+      </c>
+      <c r="C25" t="s">
+        <v>331</v>
+      </c>
+      <c r="D25" t="s">
+        <v>332</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A26" s="6">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>333</v>
+      </c>
+      <c r="C26" t="s">
+        <v>334</v>
+      </c>
+      <c r="D26" t="s">
+        <v>335</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="29" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="I29" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>336</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I30" t="s">
+        <v>264</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I31" t="s">
+        <v>267</v>
+      </c>
+      <c r="J31" t="s">
+        <v>268</v>
+      </c>
+      <c r="K31" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I32" t="s">
+        <v>270</v>
+      </c>
+      <c r="J32" t="s">
+        <v>271</v>
+      </c>
+      <c r="K32" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="33" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I33" t="s">
+        <v>273</v>
+      </c>
+      <c r="J33" t="s">
+        <v>274</v>
+      </c>
+      <c r="K33" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="34" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I34" t="s">
+        <v>276</v>
+      </c>
+      <c r="J34" t="s">
+        <v>277</v>
+      </c>
+      <c r="K34" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="35" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I35" t="s">
+        <v>279</v>
+      </c>
+      <c r="J35" t="s">
+        <v>280</v>
+      </c>
+      <c r="K35" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I36" t="s">
+        <v>282</v>
+      </c>
+      <c r="J36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="37" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I37" t="s">
+        <v>284</v>
+      </c>
+      <c r="J37" t="s">
+        <v>285</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="38" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I38" t="s">
+        <v>288</v>
+      </c>
+      <c r="J38" t="s">
+        <v>289</v>
+      </c>
+      <c r="K38" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="39" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>291</v>
+      </c>
+      <c r="J39" t="s">
+        <v>292</v>
+      </c>
+      <c r="K39" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="40" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I40" t="s">
+        <v>294</v>
+      </c>
+      <c r="J40" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I41" t="s">
+        <v>297</v>
+      </c>
+      <c r="J41" t="s">
+        <v>298</v>
+      </c>
+      <c r="K41" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="42" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I42" t="s">
+        <v>300</v>
+      </c>
+      <c r="J42" t="s">
+        <v>301</v>
+      </c>
+      <c r="K42" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="43" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I43" t="s">
+        <v>303</v>
+      </c>
+      <c r="J43" t="s">
+        <v>304</v>
+      </c>
+      <c r="K43" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="44" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I44" t="s">
+        <v>306</v>
+      </c>
+      <c r="J44" t="s">
+        <v>307</v>
+      </c>
+      <c r="K44" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="45" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I45" t="s">
+        <v>309</v>
+      </c>
+      <c r="J45" t="s">
+        <v>310</v>
+      </c>
+      <c r="K45" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="46" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I46" t="s">
+        <v>311</v>
+      </c>
+      <c r="J46" t="s">
+        <v>312</v>
+      </c>
+      <c r="K46" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="47" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I47" t="s">
+        <v>314</v>
+      </c>
+      <c r="J47" t="s">
+        <v>315</v>
+      </c>
+      <c r="K47" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="48" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I48" t="s">
+        <v>317</v>
+      </c>
+      <c r="J48" t="s">
+        <v>318</v>
+      </c>
+      <c r="K48" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I49" t="s">
+        <v>320</v>
+      </c>
+      <c r="J49" t="s">
+        <v>321</v>
+      </c>
+      <c r="K49" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I50" t="s">
+        <v>323</v>
+      </c>
+      <c r="J50" t="s">
+        <v>324</v>
+      </c>
+      <c r="K50" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I51" t="s">
+        <v>326</v>
+      </c>
+      <c r="J51" t="s">
+        <v>327</v>
+      </c>
+      <c r="K51" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I52" t="s">
+        <v>62</v>
+      </c>
+      <c r="J52" t="s">
+        <v>328</v>
+      </c>
+      <c r="K52" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>338</v>
+      </c>
+      <c r="I53" t="s">
+        <v>330</v>
+      </c>
+      <c r="J53" t="s">
+        <v>331</v>
+      </c>
+      <c r="K53" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>339</v>
+      </c>
+      <c r="I54" t="s">
+        <v>333</v>
+      </c>
+      <c r="J54" t="s">
+        <v>334</v>
+      </c>
+      <c r="K54" t="s">
+        <v>335</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13391,11 +13391,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="235a4505-cbfa-404f-a904-182fe34b6a24" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13587,26 +13588,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="235a4505-cbfa-404f-a904-182fe34b6a24" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{364F3D7B-FFFE-42E8-AA6E-3F707F1CB0D0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B1347B-0EB3-42BE-9499-F6765722E888}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="235a4505-cbfa-404f-a904-182fe34b6a24"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13630,9 +13622,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B1347B-0EB3-42BE-9499-F6765722E888}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{364F3D7B-FFFE-42E8-AA6E-3F707F1CB0D0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="235a4505-cbfa-404f-a904-182fe34b6a24"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Proyectores QR.xlsx
+++ b/Proyectores QR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2smra\Downloads\proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B7D42A-88BC-4E4D-9B80-513D3B890BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85D1F57-A7CD-42E9-954A-769EC38477B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25485" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="922">
   <si>
     <t>Numero</t>
   </si>
@@ -2905,7 +2905,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3139,6 +3139,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF92D050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3446,7 +3454,7 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -3676,6 +3684,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="60% - Énfasis6" xfId="4" builtinId="52"/>
@@ -6415,8 +6427,39 @@
       <c r="K58" s="59"/>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="E59" s="59"/>
-      <c r="K59" s="59"/>
+      <c r="A59" s="110" t="s">
+        <v>895</v>
+      </c>
+      <c r="B59" s="110" t="s">
+        <v>861</v>
+      </c>
+      <c r="C59" s="110" t="s">
+        <v>896</v>
+      </c>
+      <c r="D59" s="110" t="s">
+        <v>897</v>
+      </c>
+      <c r="E59" s="110"/>
+      <c r="F59" s="111"/>
+      <c r="G59" s="110" t="s">
+        <v>898</v>
+      </c>
+      <c r="H59" s="110" t="s">
+        <v>748</v>
+      </c>
+      <c r="I59" s="110" t="s">
+        <v>899</v>
+      </c>
+      <c r="J59" s="110"/>
+      <c r="K59" s="112" t="s">
+        <v>849</v>
+      </c>
+      <c r="L59" s="110" t="s">
+        <v>148</v>
+      </c>
+      <c r="M59" s="113" t="s">
+        <v>900</v>
+      </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
@@ -6624,12 +6667,14 @@
     <hyperlink ref="M55" r:id="rId72" xr:uid="{2018BBF1-AC41-4F7E-9F34-7044676E2820}"/>
     <hyperlink ref="M57" r:id="rId73" xr:uid="{51B291A1-F46A-4AB5-82E9-E6D2B3DFF468}"/>
     <hyperlink ref="M9" r:id="rId74" xr:uid="{37CD2CF8-5183-4341-A014-09F367A8D9B8}"/>
+    <hyperlink ref="K59" r:id="rId75" display="https://www.pccomponentes.com/benq-mw550-proyector-3600-lumenes-ansi-dlp-wxga" xr:uid="{97F02801-DB92-4227-A787-5EB641FF774F}"/>
+    <hyperlink ref="M59" r:id="rId76" xr:uid="{998A1A6E-8A3E-4AED-A694-DF9B016BE052}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId75"/>
-  <drawing r:id="rId76"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId77"/>
+  <drawing r:id="rId78"/>
   <tableParts count="1">
-    <tablePart r:id="rId77"/>
+    <tablePart r:id="rId79"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13391,12 +13436,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="235a4505-cbfa-404f-a904-182fe34b6a24" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13588,17 +13632,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="235a4505-cbfa-404f-a904-182fe34b6a24" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B1347B-0EB3-42BE-9499-F6765722E888}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{364F3D7B-FFFE-42E8-AA6E-3F707F1CB0D0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="235a4505-cbfa-404f-a904-182fe34b6a24"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13622,17 +13675,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{364F3D7B-FFFE-42E8-AA6E-3F707F1CB0D0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B1347B-0EB3-42BE-9499-F6765722E888}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="235a4505-cbfa-404f-a904-182fe34b6a24"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>